--- a/artfynd/A 60129-2025 artfynd.xlsx
+++ b/artfynd/A 60129-2025 artfynd.xlsx
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
